--- a/artfynd/A 12291-2022 artfynd.xlsx
+++ b/artfynd/A 12291-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12291-2022 artfynd.xlsx
+++ b/artfynd/A 12291-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101755497</v>
+        <v>101754859</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429709.898403946</v>
+        <v>429730</v>
       </c>
       <c r="R2" t="n">
-        <v>6697067.589413598</v>
+        <v>6697049</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101754859</v>
+        <v>101755971</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avradsberg, Malung-Sälen, Dlr</t>
+          <t>Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429729.8344770718</v>
+        <v>429681</v>
       </c>
       <c r="R3" t="n">
-        <v>6697048.916091012</v>
+        <v>6696864</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101756251</v>
+        <v>101756082</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429682.9651049906</v>
+        <v>429648</v>
       </c>
       <c r="R4" t="n">
-        <v>6696801.700275921</v>
+        <v>6696812</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101755391</v>
+        <v>101755025</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429741.5896872302</v>
+        <v>429718</v>
       </c>
       <c r="R5" t="n">
-        <v>6697067.964345447</v>
+        <v>6697047</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,51 +1067,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101756113</v>
+        <v>101755497</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malung-Sälen, Dlr</t>
+          <t>Avradsberg, Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>429638.0907752479</v>
+        <v>429709</v>
       </c>
       <c r="R6" t="n">
-        <v>6696810.972668471</v>
+        <v>6697068</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,51 +1165,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101755025</v>
+        <v>101755039</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Avradsberg, Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>429717.9095258462</v>
+        <v>429719</v>
       </c>
       <c r="R7" t="n">
-        <v>6697046.675706697</v>
+        <v>6697048</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1235,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1264,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101755551</v>
+        <v>101755391</v>
       </c>
       <c r="B8" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1275,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>429704.9113564686</v>
+        <v>429742</v>
       </c>
       <c r="R8" t="n">
-        <v>6697065.708989455</v>
+        <v>6697068</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1333,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1362,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101755564</v>
+        <v>101755540</v>
       </c>
       <c r="B9" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,36 +1373,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Avradsberg, Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>429702.9127085466</v>
+        <v>429712</v>
       </c>
       <c r="R9" t="n">
-        <v>6697064.75919517</v>
+        <v>6697070</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,19 +1431,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,51 +1460,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101755546</v>
+        <v>101756113</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Avradsberg, Malung-Sälen, Dlr</t>
+          <t>Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>429708.9469202782</v>
+        <v>429638</v>
       </c>
       <c r="R10" t="n">
-        <v>6697069.584840851</v>
+        <v>6696811</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1654,19 +1529,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101755039</v>
+        <v>101756192</v>
       </c>
       <c r="B11" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,36 +1569,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Avradsberg, Malung-Sälen, Dlr</t>
+          <t>Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>429718.9279856171</v>
+        <v>429683</v>
       </c>
       <c r="R11" t="n">
-        <v>6697048.138746137</v>
+        <v>6696775</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,19 +1627,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,37 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101756082</v>
+        <v>101756251</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>429648.0177523758</v>
+        <v>429683</v>
       </c>
       <c r="R12" t="n">
-        <v>6696812.263122837</v>
+        <v>6696802</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,19 +1725,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,37 +1754,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101755379</v>
+        <v>101755546</v>
       </c>
       <c r="B13" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>429736.3755743605</v>
+        <v>429709</v>
       </c>
       <c r="R13" t="n">
-        <v>6697079.927263182</v>
+        <v>6697070</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1994,19 +1823,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,51 +1852,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101755540</v>
+        <v>101756319</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Avradsberg, Malung-Sälen, Dlr</t>
+          <t>Malung-Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>429711.9257505627</v>
+        <v>429675</v>
       </c>
       <c r="R14" t="n">
-        <v>6697070.021405878</v>
+        <v>6696861</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,19 +1921,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,37 +1950,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101755234</v>
+        <v>101755379</v>
       </c>
       <c r="B15" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6459</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>429731.7303993647</v>
+        <v>429737</v>
       </c>
       <c r="R15" t="n">
-        <v>6697070.132200243</v>
+        <v>6697080</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,19 +2019,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,6 +2045,411 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>101755551</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Avradsberg, Malung-Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>429705</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697066</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101755234</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Avradsberg, Malung-Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>429731</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697070</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>101755564</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Avradsberg, Malung-Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>429703</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697065</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>94410348</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hembäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>429756</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6696996</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gisela Åberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gisela Åberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12291-2022 artfynd.xlsx
+++ b/artfynd/A 12291-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101754859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101756082</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755497</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969916</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968104</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1746,6 +1801,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755039</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1843,6 +1903,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959006</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961827</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755391</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755540</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101756113</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101756192</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2434,6 +2524,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101756251</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2531,6 +2626,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956404</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965775</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2735,6 +2840,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755546</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2833,6 +2943,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101756319</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2934,6 +3049,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959409</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3031,6 +3151,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959807</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960548</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3230,6 +3360,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755379</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966822</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3424,6 +3564,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956613</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3526,6 +3671,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958564</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3627,6 +3777,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967246</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3725,6 +3880,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755551</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3823,6 +3983,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755234</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3925,6 +4090,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965553</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968295</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4128,6 +4303,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955568</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4229,6 +4409,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962757</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4330,6 +4515,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956815</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4431,6 +4621,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968297</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4530,6 +4725,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101755564</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4640,8 +4840,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94410348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 12291-2022 artfynd.xlsx
+++ b/artfynd/A 12291-2022 artfynd.xlsx
@@ -889,7 +889,7 @@
         <v>134956813</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>134968296</v>
       </c>
       <c r="B5" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>134963800</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>134969916</v>
       </c>
       <c r="B10" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>134968104</v>
       </c>
       <c r="B11" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>134959006</v>
       </c>
       <c r="B13" t="n">
-        <v>96413</v>
+        <v>96457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>134961827</v>
       </c>
       <c r="B14" t="n">
-        <v>92199</v>
+        <v>92241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>134956404</v>
       </c>
       <c r="B20" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>134965775</v>
       </c>
       <c r="B21" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>134959409</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>134959807</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>134960548</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>134966822</v>
       </c>
       <c r="B28" t="n">
-        <v>75468</v>
+        <v>75504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>134956613</v>
       </c>
       <c r="B29" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>134958564</v>
       </c>
       <c r="B30" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>134967246</v>
       </c>
       <c r="B31" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>134965553</v>
       </c>
       <c r="B34" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>134955568</v>
       </c>
       <c r="B36" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>134962757</v>
       </c>
       <c r="B37" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>134956815</v>
       </c>
       <c r="B38" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>134968297</v>
       </c>
       <c r="B39" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
